--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N40_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N40_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.76209885703475</v>
+        <v>4.673841064268148</v>
       </c>
       <c r="D2" t="n">
-        <v>28.71300388024245</v>
+        <v>4.665863130539399</v>
       </c>
       <c r="E2" t="n">
-        <v>10.95524863000163</v>
+        <v>1.780227902375265</v>
       </c>
       <c r="F2" t="n">
-        <v>6.873915789567454</v>
+        <v>1.117011315804711</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>6.85160159703149</v>
+        <v>1.113385259517617</v>
       </c>
       <c r="D3" t="n">
-        <v>14.96517230110754</v>
+        <v>2.431840498929976</v>
       </c>
       <c r="E3" t="n">
-        <v>10.95524863000163</v>
+        <v>1.780227902375265</v>
       </c>
       <c r="F3" t="n">
-        <v>6.873915789567454</v>
+        <v>1.117011315804711</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
